--- a/Tagihan/2026/September/Pa Udin.xlsx
+++ b/Tagihan/2026/September/Pa Udin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{167AC531-DF2A-47B9-950F-136173B113C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CD5D98-33C5-43E2-A2CA-5E9FCF42DB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,13 +81,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Paket Ezviz TY1 Pro 3mp + Memori 32GB</t>
-  </si>
-  <si>
-    <t>Pkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kepada Tuan/Nyonya  </t>
+    <t>Lot</t>
   </si>
   <si>
     <r>
@@ -122,6 +116,12 @@
       </rPr>
       <t>2026</t>
     </r>
+  </si>
+  <si>
+    <t>Kepada Tuan/Nyonya  Sekolah Alam</t>
+  </si>
+  <si>
+    <t>Setting Dan Konfigurasi Kamera Ezviz</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1085,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G13" s="48"/>
       <c r="N13" s="6" t="s">
@@ -1131,20 +1131,20 @@
         <v>1</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" s="26">
-        <v>850000</v>
+        <v>100000</v>
       </c>
       <c r="G17" s="27">
         <f>D17*F17</f>
-        <v>850000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1253,7 +1253,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="30">
         <f>SUM(G17:G29)</f>
-        <v>850000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
